--- a/files/BNM_Loan_Book_Quarter_End.xlsx
+++ b/files/BNM_Loan_Book_Quarter_End.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loan Book QE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,19 +26,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -51,12 +58,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,30 +79,45 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D0D7E2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,406 +483,1088 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BNM Quarterly Loan Book - Q1 FY2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Gross balance (MYR)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Stage 1</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Stage 2</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Stage 3</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>NPL %</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>ECL provision</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Outlook</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>BNM Loan Book Quarter End</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source file: BNM_Loan_Book_Quarter_End.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Retail-Mortgage</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>3,153,000,000</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2,607,175,893</t>
+          <t>Drawdown</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>307,319,854</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>238,504,253</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>7.56%</t>
+          <t>Repayment</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>633,000</t>
+          <t>Closing</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Deteriorating</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Retail-Auto</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2,942,000,000</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2,630,441,462</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>238,885,724</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>72,672,814</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2.47%</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>388,000</t>
-        </is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>267002229</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>267002229.2864783</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1329222</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5779259</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>262552192</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Improving</t>
+          <t>Initial drawdown</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Retail-Personal</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>4,760,000,000</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>4,045,861,413</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>292,253,214</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>421,885,373</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>8.86%</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>533,000</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>262552192</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="7" t="n">
+        <v>1307068</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>5757105</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>258102155</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SME-Working-Cap</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2,386,000,000</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>1,879,191,634</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>275,895,068</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>230,913,298</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>9.68%</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>910,000</t>
-        </is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>258102155</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>1284914</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5734951</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>253652118</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Deteriorating</t>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>SME-Term</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>4,867,000,000</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>4,499,068,806</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>546,003,744</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>-178,072,550</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>-3.66%</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>615,000</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Improving</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>253652118</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="7" t="n">
+        <v>1262760</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5712798</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>249202081</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Corporate-Term</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>3,910,000,000</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>3,497,370,687</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>312,257,462</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>100,371,851</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>2.57%</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>807,000</t>
-        </is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>249202081</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>1240607</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5690644</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>244752044</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Deteriorating</t>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Corporate-RCF</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>8,971,000,000</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>8,180,308,167</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>715,792,698</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>74,899,135</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>0.83%</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>372,000</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Deteriorating</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>244752044</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="7" t="n">
+        <v>1218453</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>5668490</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>240302006</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Trade-Finance</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>9,081,000,000</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>7,705,996,719</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>538,124,543</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>836,878,738</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>9.22%</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>877,000</t>
-        </is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>240302006</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>1196299</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>5646337</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>235851969</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Improving</t>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>235851969</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="7" t="n">
+        <v>1174146</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>5624183</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>231401932</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>231401932</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="5" t="n">
+        <v>1151992</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>5602029</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>226951895</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>226951895</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="7" t="n">
+        <v>1129838</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5579875</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>222501858</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>222501858</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>1107685</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5557722</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>218051821</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>218051821</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="7" t="n">
+        <v>1085531</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>5535568</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>213601783</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>213601783</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="5" t="n">
+        <v>1063377</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>5513414</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>209151746</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>209151746</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="7" t="n">
+        <v>1041224</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>5491261</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>204701709</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>204701709</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="n">
+        <v>1019070</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>5469107</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>200251672</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>200251672</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="n">
+        <v>996916</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>5446953</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>195801635</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>195801635</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>974762</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>5424800</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>191351598</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>191351598</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="7" t="n">
+        <v>952609</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>5402646</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>186901561</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>186901561</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="5" t="n">
+        <v>930455</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>5380492</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>182451523</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>182451523</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="7" t="n">
+        <v>908301</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>5358339</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>178001486</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>178001486</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="5" t="n">
+        <v>886148</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>5336185</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>173551449</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>173551449</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="7" t="n">
+        <v>863994</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>5314031</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>169101412</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>169101412</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="5" t="n">
+        <v>841840</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>5291877</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>164651375</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>164651375</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="7" t="n">
+        <v>819687</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>5269724</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>160201338</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>160201338</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="5" t="n">
+        <v>797533</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>5247570</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>155751300</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>155751300</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="7" t="n">
+        <v>775379</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>5225416</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>151301263</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>151301263</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="5" t="n">
+        <v>753226</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>5203263</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>146851226</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>146851226</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="7" t="n">
+        <v>731072</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>5181109</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>142401189</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>142401189</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="5" t="n">
+        <v>708918</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>5158955</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>137951152</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>137951152</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="7" t="n">
+        <v>686764</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>5136802</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>133501115</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>133501115</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="5" t="n">
+        <v>664611</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>5114648</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>129051077</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>129051077</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="7" t="n">
+        <v>642457</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>5092494</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>124601040</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>124601040</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="5" t="n">
+        <v>620303</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>5070341</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>120151003</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>120151003</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="7" t="n">
+        <v>598150</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>5048187</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>115700966</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>115700966</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="5" t="n">
+        <v>575996</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>5026033</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>111250929</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>111250929</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="7" t="n">
+        <v>553842</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>4450037</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>5003879</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>106800892</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Standard amortising schedule</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
